--- a/AAII_Financials/Quarterly/ANAB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANAB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
   <si>
     <t>ANAB</t>
   </si>
@@ -833,8 +833,8 @@
       <c r="D8" s="3">
         <v>25600</v>
       </c>
-      <c r="E8" s="3">
-        <v>108200</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F8" s="3">
         <v>76300</v>
@@ -845,8 +845,8 @@
       <c r="H8" s="3">
         <v>27800</v>
       </c>
-      <c r="I8" s="3">
-        <v>43100</v>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J8" s="3">
         <v>30000</v>
@@ -955,8 +955,8 @@
       <c r="D9" s="3">
         <v>34000</v>
       </c>
-      <c r="E9" s="3">
-        <v>25600</v>
+      <c r="E9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F9" s="3">
         <v>31400</v>
@@ -967,8 +967,8 @@
       <c r="H9" s="3">
         <v>41200</v>
       </c>
-      <c r="I9" s="3">
-        <v>42600</v>
+      <c r="I9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J9" s="3">
         <v>42200</v>
@@ -1077,8 +1077,8 @@
       <c r="D10" s="3">
         <v>-8400</v>
       </c>
-      <c r="E10" s="3">
-        <v>82700</v>
+      <c r="E10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F10" s="3">
         <v>44900</v>
@@ -1089,8 +1089,8 @@
       <c r="H10" s="3">
         <v>-13400</v>
       </c>
-      <c r="I10" s="3">
-        <v>500</v>
+      <c r="I10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J10" s="3">
         <v>-12200</v>
@@ -1243,8 +1243,8 @@
       <c r="D12" s="3">
         <v>34000</v>
       </c>
-      <c r="E12" s="3">
-        <v>25600</v>
+      <c r="E12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F12" s="3">
         <v>31400</v>
@@ -1255,8 +1255,8 @@
       <c r="H12" s="3">
         <v>41200</v>
       </c>
-      <c r="I12" s="3">
-        <v>42600</v>
+      <c r="I12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J12" s="3">
         <v>42200</v>
@@ -1772,8 +1772,8 @@
       <c r="D17" s="3">
         <v>60200</v>
       </c>
-      <c r="E17" s="3">
-        <v>41300</v>
+      <c r="E17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F17" s="3">
         <v>41600</v>
@@ -1784,8 +1784,8 @@
       <c r="H17" s="3">
         <v>55300</v>
       </c>
-      <c r="I17" s="3">
-        <v>52800</v>
+      <c r="I17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J17" s="3">
         <v>52800</v>
@@ -1894,8 +1894,8 @@
       <c r="D18" s="3">
         <v>-34600</v>
       </c>
-      <c r="E18" s="3">
-        <v>66900</v>
+      <c r="E18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F18" s="3">
         <v>34700</v>
@@ -1906,8 +1906,8 @@
       <c r="H18" s="3">
         <v>-27500</v>
       </c>
-      <c r="I18" s="3">
-        <v>-9700</v>
+      <c r="I18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J18" s="3">
         <v>-22800</v>
@@ -2060,8 +2060,8 @@
       <c r="D20" s="3">
         <v>0</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>4</v>
@@ -2072,8 +2072,8 @@
       <c r="H20" s="3">
         <v>-1900</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -2183,7 +2183,7 @@
         <v>-34500</v>
       </c>
       <c r="E21" s="3">
-        <v>67000</v>
+        <v>100</v>
       </c>
       <c r="F21" s="3">
         <v>34800</v>
@@ -2195,7 +2195,7 @@
         <v>-25500</v>
       </c>
       <c r="I21" s="3">
-        <v>-9500</v>
+        <v>100</v>
       </c>
       <c r="J21" s="3">
         <v>-22600</v>
@@ -2304,8 +2304,8 @@
       <c r="D22" s="3">
         <v>20900</v>
       </c>
-      <c r="E22" s="3">
-        <v>19700</v>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F22" s="3">
         <v>22500</v>
@@ -2316,8 +2316,8 @@
       <c r="H22" s="3">
         <v>18100</v>
       </c>
-      <c r="I22" s="3">
-        <v>17400</v>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J22" s="3">
         <v>15400</v>
@@ -2426,8 +2426,8 @@
       <c r="D23" s="3">
         <v>-52800</v>
       </c>
-      <c r="E23" s="3">
-        <v>49700</v>
+      <c r="E23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F23" s="3">
         <v>15100</v>
@@ -2438,8 +2438,8 @@
       <c r="H23" s="3">
         <v>-39300</v>
       </c>
-      <c r="I23" s="3">
-        <v>-21800</v>
+      <c r="I23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J23" s="3">
         <v>-32900</v>
@@ -2548,8 +2548,8 @@
       <c r="D24" s="3">
         <v>0</v>
       </c>
-      <c r="E24" s="3">
-        <v>100</v>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>4</v>
@@ -2560,8 +2560,8 @@
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>4</v>
@@ -2792,8 +2792,8 @@
       <c r="D26" s="3">
         <v>-52900</v>
       </c>
-      <c r="E26" s="3">
-        <v>49600</v>
+      <c r="E26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F26" s="3">
         <v>15100</v>
@@ -2804,8 +2804,8 @@
       <c r="H26" s="3">
         <v>-39300</v>
       </c>
-      <c r="I26" s="3">
-        <v>-21800</v>
+      <c r="I26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J26" s="3">
         <v>-32900</v>
@@ -2914,8 +2914,8 @@
       <c r="D27" s="3">
         <v>-52900</v>
       </c>
-      <c r="E27" s="3">
-        <v>49600</v>
+      <c r="E27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F27" s="3">
         <v>15100</v>
@@ -2926,8 +2926,8 @@
       <c r="H27" s="3">
         <v>-39300</v>
       </c>
-      <c r="I27" s="3">
-        <v>-21800</v>
+      <c r="I27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J27" s="3">
         <v>-32900</v>
@@ -3524,8 +3524,8 @@
       <c r="D32" s="3">
         <v>0</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>4</v>
@@ -3536,8 +3536,8 @@
       <c r="H32" s="3">
         <v>1900</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -3646,8 +3646,8 @@
       <c r="D33" s="3">
         <v>-52900</v>
       </c>
-      <c r="E33" s="3">
-        <v>49600</v>
+      <c r="E33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F33" s="3">
         <v>15100</v>
@@ -3658,8 +3658,8 @@
       <c r="H33" s="3">
         <v>-39300</v>
       </c>
-      <c r="I33" s="3">
-        <v>-21800</v>
+      <c r="I33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J33" s="3">
         <v>-32900</v>
@@ -3890,8 +3890,8 @@
       <c r="D35" s="3">
         <v>-52900</v>
       </c>
-      <c r="E35" s="3">
-        <v>49600</v>
+      <c r="E35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F35" s="3">
         <v>15100</v>
@@ -3902,8 +3902,8 @@
       <c r="H35" s="3">
         <v>-39300</v>
       </c>
-      <c r="I35" s="3">
-        <v>-21800</v>
+      <c r="I35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J35" s="3">
         <v>-32900</v>
@@ -4228,7 +4228,7 @@
         <v>248500</v>
       </c>
       <c r="E41" s="3">
-        <v>238200</v>
+        <v>138200</v>
       </c>
       <c r="F41" s="3">
         <v>109800</v>
@@ -4240,7 +4240,7 @@
         <v>98600</v>
       </c>
       <c r="I41" s="3">
-        <v>123100</v>
+        <v>23100</v>
       </c>
       <c r="J41" s="3">
         <v>191600</v>
@@ -4715,8 +4715,8 @@
       <c r="D45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>4</v>
+      <c r="E45" s="3">
+        <v>104800</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>4</v>
@@ -4727,8 +4727,8 @@
       <c r="H45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
+      <c r="I45" s="3">
+        <v>104600</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
@@ -5082,7 +5082,7 @@
         <v>13300</v>
       </c>
       <c r="E48" s="3">
-        <v>13900</v>
+        <v>12600</v>
       </c>
       <c r="F48" s="3">
         <v>14500</v>
@@ -5094,7 +5094,7 @@
         <v>15700</v>
       </c>
       <c r="I48" s="3">
-        <v>16200</v>
+        <v>14500</v>
       </c>
       <c r="J48" s="3">
         <v>16600</v>
@@ -5570,7 +5570,7 @@
         <v>300</v>
       </c>
       <c r="E52" s="3">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="F52" s="3">
         <v>300</v>
@@ -5582,7 +5582,7 @@
         <v>300</v>
       </c>
       <c r="I52" s="3">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="J52" s="3">
         <v>300</v>
@@ -8634,8 +8634,8 @@
       <c r="D81" s="3">
         <v>-52900</v>
       </c>
-      <c r="E81" s="3">
-        <v>49600</v>
+      <c r="E81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F81" s="3">
         <v>15100</v>
@@ -8646,8 +8646,8 @@
       <c r="H81" s="3">
         <v>-39300</v>
       </c>
-      <c r="I81" s="3">
-        <v>-21800</v>
+      <c r="I81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J81" s="3">
         <v>-32900</v>
@@ -8800,8 +8800,8 @@
       <c r="D83" s="3">
         <v>600</v>
       </c>
-      <c r="E83" s="3">
-        <v>600</v>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F83" s="3">
         <v>600</v>
@@ -9532,8 +9532,8 @@
       <c r="D89" s="3">
         <v>-25900</v>
       </c>
-      <c r="E89" s="3">
-        <v>98000</v>
+      <c r="E89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F89" s="3">
         <v>-27400</v>
@@ -9544,8 +9544,8 @@
       <c r="H89" s="3">
         <v>-10700</v>
       </c>
-      <c r="I89" s="3">
-        <v>-66700</v>
+      <c r="I89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J89" s="3">
         <v>-10100</v>
@@ -9698,8 +9698,8 @@
       <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -9710,8 +9710,8 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3">
-        <v>-300</v>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -10064,8 +10064,8 @@
       <c r="D94" s="3">
         <v>35000</v>
       </c>
-      <c r="E94" s="3">
-        <v>73500</v>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F94" s="3">
         <v>103300</v>
@@ -10076,8 +10076,8 @@
       <c r="H94" s="3">
         <v>14800</v>
       </c>
-      <c r="I94" s="3">
-        <v>-29400</v>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J94" s="3">
         <v>58600</v>
@@ -10718,8 +10718,8 @@
       <c r="D100" s="3">
         <v>1200</v>
       </c>
-      <c r="E100" s="3">
-        <v>-43100</v>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F100" s="3">
         <v>-10400</v>
@@ -10730,8 +10730,8 @@
       <c r="H100" s="3">
         <v>-28600</v>
       </c>
-      <c r="I100" s="3">
-        <v>27600</v>
+      <c r="I100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J100" s="3">
         <v>71200</v>
@@ -10963,7 +10963,7 @@
         <v>10300</v>
       </c>
       <c r="E102" s="3">
-        <v>128400</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
         <v>65500</v>
@@ -10975,7 +10975,7 @@
         <v>-24400</v>
       </c>
       <c r="I102" s="3">
-        <v>-68500</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
         <v>119800</v>
